--- a/public/templates/cfo_ai_upload_template.xlsx
+++ b/public/templates/cfo_ai_upload_template.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Trading" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="DIO" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Trial Balance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Field Reference" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trading" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DIO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trial Balance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Field Reference" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,11 +23,11 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0;-#,##0;&quot;—&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;-#,##0.00;&quot;—&quot;"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="167" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,11 +58,6 @@
       <i val="1"/>
       <color rgb="009CA3AF"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="009CA3AF"/>
-      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -117,13 +112,16 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -138,7 +136,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -243,7 +240,7 @@
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>NIV in RON. Revenue gross of discounts, minus VAT.</t>
+        <t>NIV in RON. Revenue net of discounts, excluding VAT.</t>
       </text>
     </comment>
     <comment ref="M1" authorId="0" shapeId="0">
@@ -617,9 +614,17 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="4" t="inlineStr"/>
+    <row r="4" ht="62" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>EXAMPLE DATA</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>All example rows in this workbook are fictional — invented customers, brands, products and figures. Replace them with your own data. Toate rândurile-exemplu din acest fișier sunt fictive — clienți, mărci, produse și cifre inventate. Înlocuiește-le cu datele tale.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -629,7 +634,7 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
@@ -641,7 +646,7 @@
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
@@ -653,7 +658,7 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
@@ -665,7 +670,7 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
@@ -677,7 +682,7 @@
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="3" t="inlineStr"/>
+      <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -688,7 +693,7 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Trading</t>
         </is>
@@ -700,7 +705,7 @@
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>DIO</t>
         </is>
@@ -712,7 +717,7 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Trial Balance</t>
         </is>
@@ -724,7 +729,7 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Field Reference</t>
         </is>
@@ -736,7 +741,7 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="3" t="inlineStr"/>
+      <c r="A16" s="6" t="inlineStr"/>
       <c r="B16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="22" customHeight="1">
@@ -747,7 +752,7 @@
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
@@ -759,31 +764,31 @@
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Capital mismatch between Trading and DIO (e.g., "Macrou" vs "MACROU"). Parser handles common variants but exact match is safest.</t>
+          <t>Capital mismatch between Trading and DIO (e.g., "Cafea" vs "CAFEA"). Parser handles common variants but exact match is safest.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Removing the empty rows 22-27 in the DIO sheet — they are STRUCTURAL. The parser locates Region 2 by row offset; deleting them silently breaks DIO.</t>
+          <t>Putting anything in column A of the DIO days block (rows 28-52) — a DIO-days row is read only when column A is empty, column B holds the category and column D holds the days.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
@@ -795,7 +800,7 @@
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="3" t="inlineStr"/>
+      <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="4" t="inlineStr"/>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -860,385 +865,385 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Canal</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Tip client</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>CLIENT_PARINTE</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>BU</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Categ_Pr</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Denumire_Produs</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>PackSize</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Sold in KG</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>GR Gross Revenue finished goods</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Net Invoice Value</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>Cost of Sales</t>
         </is>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Gross Margin</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>KA</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>AUCHAN</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>RETAILER A</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>KA</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>AUCHAN</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>Diverse</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>LEGUME CONSERVATE</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>ROUA</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Fasole alba in sapte ape 400g</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>400g</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>8420</v>
-      </c>
-      <c r="K2" s="9" t="n">
-        <v>195000</v>
-      </c>
-      <c r="L2" s="9" t="n">
-        <v>184000</v>
-      </c>
-      <c r="M2" s="9" t="n">
-        <v>145600</v>
-      </c>
-      <c r="N2" s="9" t="n">
-        <v>38400</v>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>RETAILER A</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Alimentare</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>CAFEA</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>MARCA A</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Cafea macinata 250g (exemplu)</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>250g</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K2" s="10" t="n">
+        <v>150000</v>
+      </c>
+      <c r="L2" s="10" t="n">
+        <v>141000</v>
+      </c>
+      <c r="M2" s="10" t="n">
+        <v>112800</v>
+      </c>
+      <c r="N2" s="10" t="n">
+        <v>28200</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>KA</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>CARREFOUR</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>RETAILER B</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>KA</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>CARREFOUR</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>Diverse</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>LEGUME CONSERVATE</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>BUCEGI</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Porumb dulce 285g</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>285g</t>
-        </is>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>6890</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>172000</v>
-      </c>
-      <c r="L3" s="9" t="n">
-        <v>162000</v>
-      </c>
-      <c r="M3" s="9" t="n">
-        <v>130700</v>
-      </c>
-      <c r="N3" s="9" t="n">
-        <v>31300</v>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>RETAILER B</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Alimentare</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>CAFEA</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>MARCA B</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>Cafea boabe 1kg (exemplu)</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>4500</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>135000</v>
+      </c>
+      <c r="L3" s="10" t="n">
+        <v>126000</v>
+      </c>
+      <c r="M3" s="10" t="n">
+        <v>100800</v>
+      </c>
+      <c r="N3" s="10" t="n">
+        <v>25200</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>DIST</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>METRO</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>DISTRIBUITOR A</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>DIST</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>METRO</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Diverse</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>TON</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>NAVODUL</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Ton in ulei 80g</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>80g</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>14200</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>405000</v>
-      </c>
-      <c r="L4" s="9" t="n">
-        <v>382000</v>
-      </c>
-      <c r="M4" s="9" t="n">
-        <v>297600</v>
-      </c>
-      <c r="N4" s="9" t="n">
-        <v>84400</v>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>DISTRIBUITOR A</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Alimentare</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>PASTE</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>MARCA C</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Paste scurte 500g (exemplu)</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>96000</v>
+      </c>
+      <c r="L4" s="10" t="n">
+        <v>90000</v>
+      </c>
+      <c r="M4" s="10" t="n">
+        <v>72000</v>
+      </c>
+      <c r="N4" s="10" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>KA</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>KAUFLAND</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>RETAILER C</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>KA</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>KAUFLAND</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Diverse</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>JELEURI</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>SCANDIA</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Jeleu fructe 200g</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>200g</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>320</v>
-      </c>
-      <c r="K5" s="9" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>RETAILER C</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Alimentare</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>CIOCOLATA</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>MARCA A</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Ciocolata neagra 100g (exemplu)</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>100g</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L5" s="10" t="n">
         <v>28000</v>
       </c>
-      <c r="L5" s="9" t="n">
-        <v>26400</v>
-      </c>
-      <c r="M5" s="9" t="n">
-        <v>27800</v>
-      </c>
-      <c r="N5" s="9" t="n">
-        <v>-1400</v>
+      <c r="M5" s="10" t="n">
+        <v>29500</v>
+      </c>
+      <c r="N5" s="10" t="n">
+        <v>-1500</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>KA</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>PROFI</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>RETAILER D</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>KA</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>PROFI</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Diverse</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>MACROU</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>ROUA</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Macrou in sos tomat 240g</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>240g</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>4220</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>89000</v>
-      </c>
-      <c r="L6" s="9" t="n">
-        <v>83500</v>
-      </c>
-      <c r="M6" s="9" t="n">
-        <v>68200</v>
-      </c>
-      <c r="N6" s="9" t="n">
-        <v>15300</v>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>RETAILER D</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Alimentare</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>OREZ</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>MARCA B</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Orez bob lung 1kg (exemplu)</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>1kg</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>45000</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>42000</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <v>35700</v>
+      </c>
+      <c r="N6" s="10" t="n">
+        <v>6300</v>
       </c>
     </row>
   </sheetData>
@@ -1268,233 +1273,205 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" t="inlineStr"/>
-      <c r="B1" s="10" t="n">
-        <v>46168</v>
-      </c>
-      <c r="D1" s="10" t="n">
-        <v>46168</v>
-      </c>
-      <c r="E1" s="10" t="n">
-        <v>46168</v>
-      </c>
-      <c r="F1" s="10" t="n">
-        <v>46168</v>
-      </c>
-      <c r="G1" s="10" t="n">
-        <v>46168</v>
-      </c>
-      <c r="H1" s="10" t="n">
-        <v>46168</v>
+      <c r="B1" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="D1" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="E1" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="F1" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="G1" s="11" t="n">
+        <v>46053</v>
+      </c>
+      <c r="H1" s="11" t="n">
+        <v>46053</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Grupa_Pr</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Stoc Cantitativ (UM)</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Stoc Valoric Standard (RON)</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>Stoc RON / UM</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>Stoc KG</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>LEGUME CONSERVATE</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="n">
-        <v>71655</v>
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>CAFEA</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n">
+        <v>40000</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="14" t="n">
-        <v>2986170.15</v>
+      <c r="D3" s="15" t="n">
+        <v>800000</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="14" t="n">
-        <v>41.67</v>
+      <c r="F3" s="15" t="n">
+        <v>20</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="13" t="n">
-        <v>394797.7</v>
+      <c r="H3" s="14" t="n">
+        <v>10000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>JELEURI</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="n">
-        <v>8693</v>
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>CIOCOLATA</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>9000</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="14" t="n">
-        <v>457738.17</v>
+      <c r="D4" s="15" t="n">
+        <v>63000</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="14" t="n">
-        <v>52.66</v>
+      <c r="F4" s="15" t="n">
+        <v>7</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="13" t="n">
-        <v>13908.8</v>
+      <c r="H4" s="14" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>TON</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>12450</v>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>PASTE</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>25000</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="14" t="n">
-        <v>823412.55</v>
+      <c r="D5" s="15" t="n">
+        <v>100000</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="14" t="n">
-        <v>66.14</v>
+      <c r="F5" s="15" t="n">
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="13" t="n">
-        <v>19887.2</v>
+      <c r="H5" s="14" t="n">
+        <v>12500</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>MACROU</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>5210</v>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>OREZ</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>6000</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="14" t="n">
-        <v>274982.1</v>
+      <c r="D6" s="15" t="n">
+        <v>42000</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="14" t="n">
-        <v>52.78</v>
+      <c r="F6" s="15" t="n">
+        <v>7</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="13" t="n">
-        <v>9402.5</v>
+      <c r="H6" s="14" t="n">
+        <v>6000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>ULEI</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>1067</v>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>CEAI</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>2000</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="14" t="n">
-        <v>177280.82</v>
+      <c r="D7" s="15" t="n">
+        <v>30000</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="14" t="n">
-        <v>166.15</v>
+      <c r="F7" s="15" t="n">
+        <v>15</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="13" t="n">
-        <v>6887.5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Selection Status:</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>CompName: 40-SF</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Cod_Articol: 7*</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Subcategorie: 3.3. DIVERS</t>
-        </is>
+      <c r="H7" s="14" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="27">
@@ -1505,253 +1482,253 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>LEGUME CONSERVATE</t>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>CAFEA</t>
         </is>
       </c>
       <c r="D28" s="17" t="n">
-        <v>73.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>MURATURI</t>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>CEAI</t>
         </is>
       </c>
       <c r="D29" s="17" t="n">
-        <v>58.5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>COMPOT</t>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>PASTE</t>
         </is>
       </c>
       <c r="D30" s="17" t="n">
-        <v>167.9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>DULCEATA</t>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>OREZ</t>
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>29.2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>JELEURI</t>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>FAINA</t>
         </is>
       </c>
       <c r="D32" s="17" t="n">
-        <v>1001.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>PASTA TOMATE</t>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>ZAHAR</t>
         </is>
       </c>
       <c r="D33" s="17" t="n">
-        <v>98.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>SUC</t>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>CIOCOLATA</t>
         </is>
       </c>
       <c r="D34" s="17" t="n">
-        <v>146.2</v>
+        <v>410</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>SUC DE ROSII</t>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>BISCUITI</t>
         </is>
       </c>
       <c r="D35" s="17" t="n">
-        <v>34.7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>SIROP</t>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>NAPOLITANE</t>
         </is>
       </c>
       <c r="D36" s="17" t="n">
-        <v>19.9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>ZACUSCA</t>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>CEREALE</t>
         </is>
       </c>
       <c r="D37" s="17" t="n">
-        <v>27.8</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>OTET</t>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>MIERE</t>
         </is>
       </c>
       <c r="D38" s="17" t="n">
-        <v>17.6</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>MUSTAR</t>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>CONDIMENTE</t>
         </is>
       </c>
       <c r="D39" s="17" t="n">
-        <v>24.1</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>SOSURI</t>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>SARE</t>
         </is>
       </c>
       <c r="D40" s="17" t="n">
-        <v>39.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>SUPE INSTANT NOODLES</t>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>APA MINERALA</t>
         </is>
       </c>
       <c r="D41" s="17" t="n">
-        <v>150.6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>PET FOOD</t>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>BAUTURI RACORITOARE</t>
         </is>
       </c>
       <c r="D42" s="17" t="n">
-        <v>30.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>ULEI</t>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>SNACKS</t>
         </is>
       </c>
       <c r="D43" s="17" t="n">
-        <v>286.6</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>TON</t>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>ALUNE SI SEMINTE</t>
         </is>
       </c>
       <c r="D44" s="17" t="n">
-        <v>194.7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>MACROU</t>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>FRUCTE USCATE</t>
         </is>
       </c>
       <c r="D45" s="17" t="n">
-        <v>64.7</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>SARDINE</t>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>CONSERVE CARNE</t>
         </is>
       </c>
       <c r="D46" s="17" t="n">
-        <v>84.90000000000001</v>
+        <v>180</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="12" t="inlineStr">
-        <is>
-          <t>HERING</t>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>LACTATE UHT</t>
         </is>
       </c>
       <c r="D47" s="17" t="n">
-        <v>118.1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t>SOMON</t>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>MALAI</t>
         </is>
       </c>
       <c r="D48" s="17" t="n">
-        <v>234</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="12" t="inlineStr">
-        <is>
-          <t>PASTRAV</t>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>LEGUMINOASE</t>
         </is>
       </c>
       <c r="D49" s="17" t="n">
-        <v>125.7</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="12" t="inlineStr">
-        <is>
-          <t>SPROT</t>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>DROJDIE</t>
         </is>
       </c>
       <c r="D50" s="17" t="n">
-        <v>105.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>FRUCTE NOBILE</t>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>ARTICOLE SEZONIERE</t>
         </is>
       </c>
       <c r="D51" s="17" t="n">
-        <v>222.1</v>
+        <v>240</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="12" t="inlineStr">
-        <is>
-          <t>ALTE MARFURI</t>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>ALTE PRODUSE</t>
         </is>
       </c>
       <c r="D52" s="17" t="n">
-        <v>102.5</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1776,22 +1753,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Cont</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Denumire</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Sold debitor</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Sold creditor</t>
         </is>
@@ -1808,10 +1785,10 @@
           <t>Capital subscris vărsat</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n">
+      <c r="C2" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="14" t="n">
+      <c r="D2" s="15" t="n">
         <v>100000</v>
       </c>
     </row>
@@ -1826,10 +1803,10 @@
           <t>Echipamente tehnologice</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n">
+      <c r="C3" s="15" t="n">
         <v>250000</v>
       </c>
-      <c r="D3" s="14" t="n">
+      <c r="D3" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1844,10 +1821,10 @@
           <t>Mărfuri</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="15" t="n">
         <v>1200000</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1862,10 +1839,10 @@
           <t>Furnizori</t>
         </is>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>450000</v>
       </c>
     </row>
@@ -1880,10 +1857,10 @@
           <t>Clienți</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="15" t="n">
         <v>340000</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1898,10 +1875,10 @@
           <t>Conturi la bănci în lei</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="15" t="n">
         <v>320000</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1916,10 +1893,10 @@
           <t>Venituri din vânzarea măr.</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>2400000</v>
       </c>
     </row>
@@ -1934,15 +1911,15 @@
           <t>Cheltuieli privind măr.</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="15" t="n">
         <v>1800000</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>OPTIONAL</t>
         </is>
@@ -1984,37 +1961,37 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2085,7 +2062,7 @@
       </c>
       <c r="F3" s="19" t="inlineStr">
         <is>
-          <t>AUCHAN</t>
+          <t>RETAILER A</t>
         </is>
       </c>
       <c r="G3" s="19" t="inlineStr">
@@ -2159,7 +2136,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AUCHAN</t>
+          <t>RETAILER A</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,7 +2173,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diverse</t>
+          <t>Alimentare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2233,7 +2210,7 @@
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>LEGUME CONSERVATE</t>
+          <t>CAFEA</t>
         </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
@@ -2270,7 +2247,7 @@
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>ROUA</t>
+          <t>MARCA A</t>
         </is>
       </c>
       <c r="G8" s="19" t="inlineStr">
@@ -2307,7 +2284,7 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>Fasole alba 400g</t>
+          <t>Cafea macinata 250g</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
@@ -2344,7 +2321,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>400g</t>
+          <t>250g</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2381,7 +2358,7 @@
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
@@ -2418,7 +2395,7 @@
       </c>
       <c r="F12" s="19" t="inlineStr">
         <is>
-          <t>195000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="G12" s="19" t="inlineStr">
@@ -2455,12 +2432,12 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>184000</t>
+          <t>141000</t>
         </is>
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>NIV — revenue net of discounts, gross of VAT</t>
+          <t>NIV — revenue net of discounts, excluding VAT</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2469,7 @@
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>145600</t>
+          <t>112800</t>
         </is>
       </c>
       <c r="G14" s="19" t="inlineStr">
@@ -2529,7 +2506,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>28200</t>
         </is>
       </c>
       <c r="G15" s="19" t="inlineStr">
@@ -2566,7 +2543,7 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>LEGUME CONSERVATE</t>
+          <t>CAFEA</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
@@ -2603,7 +2580,7 @@
       </c>
       <c r="F17" s="19" t="inlineStr">
         <is>
-          <t>71655</t>
+          <t>40000</t>
         </is>
       </c>
       <c r="G17" s="19" t="inlineStr">
@@ -2640,7 +2617,7 @@
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>2986170</t>
+          <t>800000</t>
         </is>
       </c>
       <c r="G18" s="19" t="inlineStr">
@@ -2677,7 +2654,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>20.00</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2714,7 +2691,7 @@
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>394798</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="G20" s="19" t="inlineStr">
@@ -2751,7 +2728,7 @@
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>JELEURI</t>
+          <t>CIOCOLATA</t>
         </is>
       </c>
       <c r="G21" s="19" t="inlineStr">
@@ -2788,7 +2765,7 @@
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>1001.7</t>
+          <t>410.0</t>
         </is>
       </c>
       <c r="G22" s="19" t="inlineStr">
